--- a/python/paper_design_cifar10/experiment_record(first)/experiment_result.xlsx
+++ b/python/paper_design_cifar10/experiment_record(first)/experiment_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="8675"/>
+    <workbookView windowWidth="23040" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>实验时间</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>50轮改一次</t>
+  </si>
+  <si>
+    <t>2020.12.15</t>
+  </si>
+  <si>
+    <t>cifar100部分内容</t>
+  </si>
+  <si>
+    <t>100轮修改一次</t>
   </si>
 </sst>
 </file>
@@ -98,14 +107,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -133,16 +150,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,6 +175,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -187,6 +212,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -194,46 +243,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -250,19 +259,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,25 +391,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,133 +409,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,15 +450,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -463,6 +463,30 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -483,15 +507,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -507,17 +522,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,10 +558,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -561,133 +570,133 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1046,8 +1055,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
@@ -1171,6 +1180,64 @@
       </c>
       <c r="J5" s="1">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>120</v>
+      </c>
+      <c r="E6">
+        <v>0.01</v>
+      </c>
+      <c r="F6">
+        <v>128</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7">
+        <v>0.01</v>
+      </c>
+      <c r="F7">
+        <v>128</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/python/paper_design_cifar10/experiment_record(first)/experiment_result.xlsx
+++ b/python/paper_design_cifar10/experiment_record(first)/experiment_result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>实验时间</t>
   </si>
@@ -42,6 +42,15 @@
     <t>lr改变情况</t>
   </si>
   <si>
+    <t>weight_decay</t>
+  </si>
+  <si>
+    <t>train_time</t>
+  </si>
+  <si>
+    <t>test_time</t>
+  </si>
+  <si>
     <t>实验结果</t>
   </si>
   <si>
@@ -85,6 +94,60 @@
   </si>
   <si>
     <t>100轮修改一次</t>
+  </si>
+  <si>
+    <t>2020.12.22</t>
+  </si>
+  <si>
+    <t>MobileNetV3_large_PAM</t>
+  </si>
+  <si>
+    <t>20轮减小1/10</t>
+  </si>
+  <si>
+    <t>2020.12.21</t>
+  </si>
+  <si>
+    <t>cifar10,感觉weight_decay设置的太大了</t>
+  </si>
+  <si>
+    <t>MobileNetV3_Small</t>
+  </si>
+  <si>
+    <t>MobileNetV3_large</t>
+  </si>
+  <si>
+    <t>过拟合严重</t>
+  </si>
+  <si>
+    <t>20轮减小1/8</t>
+  </si>
+  <si>
+    <t>MobileNetV3_Small_PAM</t>
+  </si>
+  <si>
+    <t>MobileNetV3_Large_PAM</t>
+  </si>
+  <si>
+    <t>20轮减小1/3</t>
+  </si>
+  <si>
+    <t>2020.12.29</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>2020.12.28</t>
+  </si>
+  <si>
+    <t>犯二了,加载一遍再跑30轮吧</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>20轮1/8</t>
   </si>
 </sst>
 </file>
@@ -122,7 +185,98 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -136,59 +290,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -197,32 +298,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,20 +312,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -259,31 +322,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -295,151 +502,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,16 +517,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -507,17 +570,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,15 +613,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -558,10 +621,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -570,141 +633,147 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1055,10 +1124,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="24.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="15.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="14.1111111111111" customWidth="1"/>
+    <col min="10" max="10" width="11.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="10.7777777777778" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1083,25 +1162,34 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>128</v>
@@ -1110,24 +1198,25 @@
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="L2" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -1139,29 +1228,30 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="L3" s="1">
         <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5">
         <v>150</v>
@@ -1176,21 +1266,22 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="1">
+        <v>22</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="L5" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>120</v>
@@ -1205,21 +1296,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="L6" s="1">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>300</v>
@@ -1234,10 +1326,452 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="1">
+        <v>25</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="L7" s="1">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>0.001</v>
+      </c>
+      <c r="F8">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.002</v>
+      </c>
+      <c r="J8">
+        <v>136</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8" s="3">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="9" spans="12:12">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>0.001</v>
+      </c>
+      <c r="F11">
+        <v>128</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.002</v>
+      </c>
+      <c r="J11">
+        <v>58</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11" s="3">
+        <v>75.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12">
+        <v>60</v>
+      </c>
+      <c r="E12">
+        <v>0.001</v>
+      </c>
+      <c r="F12">
+        <v>128</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.002</v>
+      </c>
+      <c r="L12" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>0.001</v>
+      </c>
+      <c r="F13">
+        <v>128</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.002</v>
+      </c>
+      <c r="J13">
+        <v>136</v>
+      </c>
+      <c r="K13">
+        <v>9</v>
+      </c>
+      <c r="L13" s="3">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="14" spans="9:12">
+      <c r="I14" s="2"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="9:12">
+      <c r="I15" s="2"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="9:12">
+      <c r="I16" s="2"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>60</v>
+      </c>
+      <c r="E17">
+        <v>0.0005</v>
+      </c>
+      <c r="F17">
+        <v>32</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J17">
+        <v>69</v>
+      </c>
+      <c r="K17">
+        <v>6</v>
+      </c>
+      <c r="L17" s="3">
+        <v>78.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>0.001</v>
+      </c>
+      <c r="F18">
+        <v>32</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J18">
+        <v>137</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
+        <v>84.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19">
+        <v>60</v>
+      </c>
+      <c r="E19">
+        <v>0.001</v>
+      </c>
+      <c r="F19">
+        <v>32</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J19">
+        <v>203</v>
+      </c>
+      <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19" s="3">
+        <v>79.46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20">
+        <v>60</v>
+      </c>
+      <c r="E20">
+        <v>0.001</v>
+      </c>
+      <c r="F20">
+        <v>32</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J20">
+        <v>126</v>
+      </c>
+      <c r="K20">
+        <v>9</v>
+      </c>
+      <c r="L20">
+        <v>84.66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>60</v>
+      </c>
+      <c r="E21">
+        <v>0.0005</v>
+      </c>
+      <c r="F21">
+        <v>32</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J21">
+        <v>182</v>
+      </c>
+      <c r="K21">
+        <v>11</v>
+      </c>
+      <c r="L21" s="3">
+        <v>79.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22">
+        <v>60</v>
+      </c>
+      <c r="E22">
+        <v>0.0005</v>
+      </c>
+      <c r="F22">
+        <v>32</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J22">
+        <v>245</v>
+      </c>
+      <c r="K22">
+        <v>15</v>
+      </c>
+      <c r="L22">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="9:9">
+      <c r="I23" s="2"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>0.001</v>
+      </c>
+      <c r="F25">
+        <v>32</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J25">
+        <v>58</v>
+      </c>
+      <c r="K25">
+        <v>7</v>
+      </c>
+      <c r="L25">
+        <v>79.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26">
+        <v>60</v>
+      </c>
+      <c r="E26">
+        <v>0.001</v>
+      </c>
+      <c r="F26">
+        <v>32</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="J26">
+        <v>449</v>
+      </c>
+      <c r="K26">
+        <v>28</v>
+      </c>
+      <c r="L26">
+        <v>69.34</v>
       </c>
     </row>
   </sheetData>
